--- a/files/venues.xlsx
+++ b/files/venues.xlsx
@@ -572,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -1804,6 +1804,50 @@
         <v>69</v>
       </c>
     </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29">
+        <v>35</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>20</v>
+      </c>
+      <c r="M29">
+        <v>10</v>
+      </c>
+      <c r="N29" t="s">
+        <v>69</v>
+      </c>
+    </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
@@ -1812,10 +1856,10 @@
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D30">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1827,22 +1871,22 @@
         <v>1</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N30" t="s">
         <v>69</v>
@@ -1856,10 +1900,10 @@
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1871,13 +1915,13 @@
         <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -1900,10 +1944,10 @@
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D32">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1941,13 +1985,13 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D33">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1959,13 +2003,13 @@
         <v>1</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -1988,10 +2032,10 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D34">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2015,10 +2059,10 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N34" t="s">
         <v>69</v>
@@ -2032,10 +2076,10 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D35">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2047,22 +2091,22 @@
         <v>1</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N35" t="s">
         <v>69</v>
@@ -2073,13 +2117,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D36">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2091,13 +2135,13 @@
         <v>1</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -2120,10 +2164,10 @@
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D37">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2135,13 +2179,13 @@
         <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -2164,22 +2208,22 @@
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D38">
-        <v>60</v>
+        <v>264</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2188,16 +2232,13 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38">
         <v>0</v>
-      </c>
-      <c r="N38" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -2208,16 +2249,16 @@
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D39">
-        <v>264</v>
+        <v>200</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2229,16 +2270,19 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="N39" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -2249,7 +2293,7 @@
         <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D40">
         <v>200</v>
@@ -2258,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2290,13 +2334,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D41">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2308,25 +2352,25 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -2337,10 +2381,10 @@
         <v>30</v>
       </c>
       <c r="C42" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D42">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2381,10 +2425,10 @@
         <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D43">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2425,22 +2469,22 @@
         <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D44">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2463,22 +2507,22 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D45">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -2487,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -2502,6 +2546,50 @@
         <v>0</v>
       </c>
       <c r="N45" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2510,10 +2598,10 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2528,10 +2616,10 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -2553,20 +2641,17 @@
       <c r="A48" t="s">
         <v>53</v>
       </c>
-      <c r="B48" t="s">
-        <v>55</v>
-      </c>
       <c r="C48" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -2575,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -2584,97 +2669,12 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N48" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>53</v>
-      </c>
-      <c r="B49" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>2</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>2</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" t="s">
-        <v>66</v>
-      </c>
-      <c r="D50">
-        <v>70</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>40</v>
-      </c>
-      <c r="M50">
-        <v>20</v>
-      </c>
-      <c r="N50" t="s">
         <v>69</v>
       </c>
     </row>
